--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -11918,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17121,6 +17121,36 @@
       </c>
       <c r="B520" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-07-08 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-07-24 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H384"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,126 @@
       <c r="H384" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:33+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>304.22</v>
+      </c>
+      <c r="C385" t="n">
+        <v>292.88</v>
+      </c>
+      <c r="D385" t="n">
+        <v>288.81</v>
+      </c>
+      <c r="E385" t="n">
+        <v>281.33</v>
+      </c>
+      <c r="F385" t="n">
+        <v>273.54</v>
+      </c>
+      <c r="G385" t="n">
+        <v>535.92</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:14+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="C386" t="n">
+        <v>289.76</v>
+      </c>
+      <c r="D386" t="n">
+        <v>288.81</v>
+      </c>
+      <c r="E386" t="n">
+        <v>281.33</v>
+      </c>
+      <c r="F386" t="n">
+        <v>273.54</v>
+      </c>
+      <c r="G386" t="n">
+        <v>535.92</v>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-17 22:32:28+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>304.56</v>
+      </c>
+      <c r="C387" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="D387" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="E387" t="n">
+        <v>283.31</v>
+      </c>
+      <c r="F387" t="n">
+        <v>273.54</v>
+      </c>
+      <c r="G387" t="n">
+        <v>535.92</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:22+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>305.94</v>
+      </c>
+      <c r="C388" t="n">
+        <v>290.09</v>
+      </c>
+      <c r="D388" t="n">
+        <v>290.74</v>
+      </c>
+      <c r="E388" t="n">
+        <v>280.51</v>
+      </c>
+      <c r="F388" t="n">
+        <v>273.54</v>
+      </c>
+      <c r="G388" t="n">
+        <v>535.92</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11918,7 +12038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17151,6 +17271,56 @@
       </c>
       <c r="B523" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-17 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17319,28 +17489,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.26601013348999</v>
+        <v>0.258606553365414</v>
       </c>
       <c r="J2" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09741892028887844</v>
+        <v>0.09396782975574769</v>
       </c>
       <c r="M2" t="n">
-        <v>4.894740528245575</v>
+        <v>4.883385664722305</v>
       </c>
       <c r="N2" t="n">
-        <v>38.82159124275507</v>
+        <v>38.58153486930993</v>
       </c>
       <c r="O2" t="n">
-        <v>6.23069749247667</v>
+        <v>6.211403615070424</v>
       </c>
       <c r="P2" t="n">
-        <v>301.4345589431946</v>
+        <v>301.5131181678369</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17397,28 +17567,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2876623008766784</v>
+        <v>0.286414913648948</v>
       </c>
       <c r="J3" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L3" t="n">
-        <v>0.134083194483898</v>
+        <v>0.1354075369410861</v>
       </c>
       <c r="M3" t="n">
-        <v>4.53357816587807</v>
+        <v>4.502461060848748</v>
       </c>
       <c r="N3" t="n">
-        <v>31.69292222558643</v>
+        <v>31.38577416430228</v>
       </c>
       <c r="O3" t="n">
-        <v>5.629646722982396</v>
+        <v>5.602300792023066</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5366513549337</v>
+        <v>283.5498945976598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17475,28 +17645,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3581393875896778</v>
+        <v>0.3700686719853087</v>
       </c>
       <c r="J4" t="n">
+        <v>387</v>
+      </c>
+      <c r="K4" t="n">
         <v>383</v>
       </c>
-      <c r="K4" t="n">
-        <v>379</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1489940690745777</v>
+        <v>0.158985742715487</v>
       </c>
       <c r="M4" t="n">
-        <v>4.970971149824047</v>
+        <v>4.984104780360034</v>
       </c>
       <c r="N4" t="n">
-        <v>43.39408070645337</v>
+        <v>43.35353262405863</v>
       </c>
       <c r="O4" t="n">
-        <v>6.587418364310359</v>
+        <v>6.584339953560921</v>
       </c>
       <c r="P4" t="n">
-        <v>273.5246899035706</v>
+        <v>273.397809776307</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17553,28 +17723,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3101105205671432</v>
+        <v>0.3157338913738537</v>
       </c>
       <c r="J5" t="n">
+        <v>387</v>
+      </c>
+      <c r="K5" t="n">
         <v>383</v>
       </c>
-      <c r="K5" t="n">
-        <v>379</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1173756892624779</v>
+        <v>0.1231194450982931</v>
       </c>
       <c r="M5" t="n">
-        <v>4.909854256738082</v>
+        <v>4.892348965682983</v>
       </c>
       <c r="N5" t="n">
-        <v>42.83447448366226</v>
+        <v>42.48844769529249</v>
       </c>
       <c r="O5" t="n">
-        <v>6.544805152459641</v>
+        <v>6.518316323660005</v>
       </c>
       <c r="P5" t="n">
-        <v>270.2689557191572</v>
+        <v>270.2091469698323</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17631,28 +17801,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2596031422207318</v>
+        <v>0.2542565384948123</v>
       </c>
       <c r="J6" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04142145301336142</v>
+        <v>0.0405614239890264</v>
       </c>
       <c r="M6" t="n">
-        <v>6.198458040626596</v>
+        <v>6.166986173854323</v>
       </c>
       <c r="N6" t="n">
-        <v>93.76705508368313</v>
+        <v>92.86587328664361</v>
       </c>
       <c r="O6" t="n">
-        <v>9.683339046201116</v>
+        <v>9.636694105690166</v>
       </c>
       <c r="P6" t="n">
-        <v>269.4021974169186</v>
+        <v>269.458563431349</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17709,28 +17879,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.254877775730505</v>
+        <v>-5.775151860849633</v>
       </c>
       <c r="J7" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K7" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2522698257861149</v>
+        <v>0.2112211445507145</v>
       </c>
       <c r="M7" t="n">
-        <v>68.90356851340135</v>
+        <v>72.17584826851727</v>
       </c>
       <c r="N7" t="n">
-        <v>6828.837218825723</v>
+        <v>7408.760949804026</v>
       </c>
       <c r="O7" t="n">
-        <v>82.63677885073766</v>
+        <v>86.07415959394565</v>
       </c>
       <c r="P7" t="n">
-        <v>453.0274817971291</v>
+        <v>447.8794668244869</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17772,7 +17942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H384"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33791,6 +33961,174 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:32:33+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-44.81563614459941,167.39166419932334</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-44.81539128428797,167.39249851133147</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-44.81508929091265,167.39328842736182</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-44.81481409245566,167.39409916846333</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-44.814541327778024,167.3949118034757</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-44.81214546909044,167.39407455249918</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:14+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-44.815638266381086,167.39166584815493</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-44.81541580256891,167.39251756469557</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-44.81508929091265,167.39328842736182</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-44.81481409245566,167.39409916846333</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-44.814541327778024,167.3949118034757</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-44.81214546909044,167.39407455249918</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-17 22:32:28+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-44.81563347272617,167.39166212301703</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-44.81541548823199,167.39251732042158</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-44.81508213976973,167.39328287008811</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-44.81479853287708,167.39408707670492</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-44.814541327778024,167.3949118034757</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-44.81214546909044,167.39407455249918</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:22+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-44.81562262806389,167.39165369565814</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-44.81541320928932,167.39251554943516</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-44.81507412420269,167.39327664105758</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-44.81482053632124,167.3941041761631</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-44.814541327778024,167.3949118034757</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-44.81214546909044,167.39407455249918</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H388"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11869,7 +11869,7 @@
         <v>271.37</v>
       </c>
       <c r="G383" t="n">
-        <v>494.16</v>
+        <v>470.93</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>271.49</v>
       </c>
       <c r="G384" t="n">
-        <v>494.16</v>
+        <v>470.93</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>273.54</v>
       </c>
       <c r="G385" t="n">
-        <v>535.92</v>
+        <v>444.55</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>273.54</v>
       </c>
       <c r="G386" t="n">
-        <v>535.92</v>
+        <v>444.55</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>273.54</v>
       </c>
       <c r="G387" t="n">
-        <v>535.92</v>
+        <v>444.55</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -12019,9 +12019,99 @@
         <v>273.54</v>
       </c>
       <c r="G388" t="n">
-        <v>535.92</v>
+        <v>444.55</v>
       </c>
       <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>307.3</v>
+      </c>
+      <c r="C389" t="n">
+        <v>289.75</v>
+      </c>
+      <c r="D389" t="n">
+        <v>291.11</v>
+      </c>
+      <c r="E389" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="F389" t="n">
+        <v>274.33</v>
+      </c>
+      <c r="G389" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:33+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="C390" t="n">
+        <v>286.55</v>
+      </c>
+      <c r="D390" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="E390" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="F390" t="n">
+        <v>270.3</v>
+      </c>
+      <c r="G390" t="n">
+        <v>261.65</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:32:49+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="C391" t="n">
+        <v>287</v>
+      </c>
+      <c r="D391" t="n">
+        <v>287.94</v>
+      </c>
+      <c r="E391" t="n">
+        <v>280.22</v>
+      </c>
+      <c r="F391" t="n">
+        <v>268.41</v>
+      </c>
+      <c r="G391" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="H391" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12038,7 +12128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17321,6 +17411,36 @@
       </c>
       <c r="B528" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -17489,28 +17609,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.258606553365414</v>
+        <v>0.2538400908544274</v>
       </c>
       <c r="J2" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09396782975574769</v>
+        <v>0.0918853216743496</v>
       </c>
       <c r="M2" t="n">
-        <v>4.883385664722305</v>
+        <v>4.872103557742717</v>
       </c>
       <c r="N2" t="n">
-        <v>38.58153486930993</v>
+        <v>38.39169782667575</v>
       </c>
       <c r="O2" t="n">
-        <v>6.211403615070424</v>
+        <v>6.196103438990972</v>
       </c>
       <c r="P2" t="n">
-        <v>301.5131181678369</v>
+        <v>301.5639538227071</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17567,28 +17687,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.286414913648948</v>
+        <v>0.2815047071511292</v>
       </c>
       <c r="J3" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K3" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1354075369410861</v>
+        <v>0.1327580101482556</v>
       </c>
       <c r="M3" t="n">
-        <v>4.502461060848748</v>
+        <v>4.498236263522157</v>
       </c>
       <c r="N3" t="n">
-        <v>31.38577416430228</v>
+        <v>31.25307949242128</v>
       </c>
       <c r="O3" t="n">
-        <v>5.602300792023066</v>
+        <v>5.590445375139737</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5498945976598</v>
+        <v>283.6022531127037</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17645,28 +17765,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3700686719853087</v>
+        <v>0.3795257914541038</v>
       </c>
       <c r="J4" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K4" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L4" t="n">
-        <v>0.158985742715487</v>
+        <v>0.1667795859905197</v>
       </c>
       <c r="M4" t="n">
-        <v>4.984104780360034</v>
+        <v>4.997187969046008</v>
       </c>
       <c r="N4" t="n">
-        <v>43.35353262405863</v>
+        <v>43.3873922068331</v>
       </c>
       <c r="O4" t="n">
-        <v>6.584339953560921</v>
+        <v>6.586910672449802</v>
       </c>
       <c r="P4" t="n">
-        <v>273.397809776307</v>
+        <v>273.2967682226234</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17723,28 +17843,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3157338913738537</v>
+        <v>0.3210211561270419</v>
       </c>
       <c r="J5" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K5" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1231194450982931</v>
+        <v>0.1281053555968017</v>
       </c>
       <c r="M5" t="n">
-        <v>4.892348965682983</v>
+        <v>4.886404464925699</v>
       </c>
       <c r="N5" t="n">
-        <v>42.48844769529249</v>
+        <v>42.2890550465273</v>
       </c>
       <c r="O5" t="n">
-        <v>6.518316323660005</v>
+        <v>6.503003540405564</v>
       </c>
       <c r="P5" t="n">
-        <v>270.2091469698323</v>
+        <v>270.1526652631119</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17801,28 +17921,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2542565384948123</v>
+        <v>0.2468907481744684</v>
       </c>
       <c r="J6" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K6" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405614239890264</v>
+        <v>0.03879161039467971</v>
       </c>
       <c r="M6" t="n">
-        <v>6.166986173854323</v>
+        <v>6.165287538416767</v>
       </c>
       <c r="N6" t="n">
-        <v>92.86587328664361</v>
+        <v>92.40452371597813</v>
       </c>
       <c r="O6" t="n">
-        <v>9.636694105690166</v>
+        <v>9.612727173699362</v>
       </c>
       <c r="P6" t="n">
-        <v>269.458563431349</v>
+        <v>269.5366213779481</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17879,28 +17999,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.775151860849633</v>
+        <v>-5.964553340365851</v>
       </c>
       <c r="J7" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K7" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2112211445507145</v>
+        <v>0.2351867278607559</v>
       </c>
       <c r="M7" t="n">
-        <v>72.17584826851727</v>
+        <v>70.26342826105221</v>
       </c>
       <c r="N7" t="n">
-        <v>7408.760949804026</v>
+        <v>6932.477374319747</v>
       </c>
       <c r="O7" t="n">
-        <v>86.07415959394565</v>
+        <v>83.26149995237743</v>
       </c>
       <c r="P7" t="n">
-        <v>447.8794668244869</v>
+        <v>449.9084146434092</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17942,7 +18062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H388"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33910,7 +34030,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>-44.81247363518002,167.39432956681415</t>
+          <t>-44.81265618523614,167.39447142583666</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -33952,7 +34072,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>-44.81247363518002,167.39432956681415</t>
+          <t>-44.81265618523614,167.39447142583666</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -33994,7 +34114,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>-44.81214546909044,167.39407455249918</t>
+          <t>-44.81286348900985,167.3946325220588</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -34036,7 +34156,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>-44.81214546909044,167.39407455249918</t>
+          <t>-44.81286348900985,167.3946325220588</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -34078,7 +34198,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>-44.81214546909044,167.39407455249918</t>
+          <t>-44.81286348900985,167.3946325220588</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -34120,10 +34240,136 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>-44.81214546909044,167.39407455249918</t>
+          <t>-44.81286348900985,167.3946325220588</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-44.81561194057017,167.39164539043782</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-44.81541588115314,167.39251762576404</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-44.81507121659498,167.39327438150772</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-44.814795310944014,167.39408457285674</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-44.814535119684,167.39490697894138</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-44.813587322005965,167.39519502404804</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:33+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-44.81563803062756,167.3916656649514</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-44.815441028105404,167.39253716769213</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-44.81506752314729,167.39327151126903</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-44.814795310944014,167.39408457285674</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-44.814566788820215,167.39493159018394</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-44.81430077988911,167.39574947822908</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:32:49+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-44.81563810921207,167.39166572601926</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-44.81543749181539,167.39253441960753</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-44.81509612771942,167.39329374036097</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-44.81482281524927,167.39410594717913</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-44.81458164109361,167.39494313243813</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-44.81427838367688,167.39573207309027</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
